--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/1413-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/1413-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D643002A-3AA7-47B3-9B77-2BECFA5E4D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B730394-94CF-4B30-95A5-278B5E81E37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{12EF97D1-2ACA-4CD7-ACE7-F89166DE2834}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{DFF4A286-41AB-4B11-AF84-7B6ABA9B21A7}"/>
   </bookViews>
   <sheets>
     <sheet name="1413-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1439,17 +1439,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6356A79D-65A0-49B2-B4CF-EFFC934A2D91}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8918B5A9-D5DE-4CE9-BD47-F95C8B9CD028}">
   <dimension ref="A1:R49"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="5.109375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="17" width="8.109375" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="2" width="6.5" customWidth="1"/>
+    <col min="3" max="3" width="10.875" customWidth="1"/>
+    <col min="4" max="17" width="10.125" customWidth="1"/>
+    <col min="18" max="18" width="11.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1477,7 +1477,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1507,7 +1507,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1603,7 +1603,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="39">
         <v>2024</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="37">
         <v>2023</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2022</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="37">
         <v>2021</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>26</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="39">
         <v>2020</v>
       </c>
@@ -1983,7 +1983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>26</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>26</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="37">
         <v>2019</v>
       </c>
@@ -2149,7 +2149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="39">
         <v>2018</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="37">
         <v>2017</v>
       </c>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="39">
         <v>2016</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="37">
         <v>2015</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="39">
         <v>2014</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="37">
         <v>2013</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>2012</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="37">
         <v>2011</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="39">
         <v>2010</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="37">
         <v>2009</v>
       </c>
@@ -2801,7 +2801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="39">
         <v>2008</v>
       </c>
@@ -2855,7 +2855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="37">
         <v>2007</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="39">
         <v>2006</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="37">
         <v>2005</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="39">
         <v>2004</v>
       </c>
@@ -3071,7 +3071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="37">
         <v>2003</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="39">
         <v>2002</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="37">
         <v>2001</v>
       </c>
@@ -3233,7 +3233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="39">
         <v>2000</v>
       </c>
@@ -3287,7 +3287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="37">
         <v>1999</v>
       </c>
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="39">
         <v>1998</v>
       </c>
@@ -3395,7 +3395,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="37">
         <v>1997</v>
       </c>
@@ -3449,7 +3449,7 @@
         <v>1.89</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="39">
         <v>1996</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="37">
         <v>1995</v>
       </c>
@@ -3557,7 +3557,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="39">
         <v>1994</v>
       </c>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="37">
         <v>1993</v>
       </c>
@@ -3665,7 +3665,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="39">
         <v>1992</v>
       </c>
@@ -3719,7 +3719,7 @@
         <v>6.22</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="37">
         <v>1991</v>
       </c>
@@ -3773,7 +3773,7 @@
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="39">
         <v>1990</v>
       </c>
@@ -3827,7 +3827,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="37">
         <v>1988</v>
       </c>
@@ -3881,7 +3881,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="39">
         <v>1986</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="37">
         <v>1985</v>
       </c>
@@ -3989,7 +3989,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="39" t="s">
         <v>32</v>
       </c>
